--- a/Planilha finalizada.xlsx
+++ b/Planilha finalizada.xlsx
@@ -694,7 +694,7 @@
     </sortState>
   </autoFilter>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="64" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"-,Negrito"&amp;22eConsignado</oddHeader>
